--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
@@ -8004,7 +8004,19 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-001</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8146,7 +8158,19 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-001</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8288,7 +8312,19 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-002</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8428,7 +8464,19 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-003</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8565,7 +8613,19 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-003</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8703,7 +8763,19 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-004</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8844,7 +8916,19 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-005</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8980,7 +9064,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9116,7 +9212,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9252,7 +9360,19 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9388,7 +9508,19 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9529,7 +9661,23 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-007</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134478
+CFTS084-134479
+CFTS084-134480
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9667,7 +9815,23 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-007</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134478
+CFTS084-134479
+CFTS084-134480
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9806,7 +9970,20 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-008</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -9944,7 +10121,20 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-008</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10084,7 +10274,19 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-009</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10226,7 +10428,19 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-009</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10365,7 +10579,19 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10506,7 +10732,19 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10648,7 +10886,19 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-011</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -10789,7 +11039,19 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-011</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -10931,7 +11193,19 @@
       </c>
       <c r="N31" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O31" s="177" t="inlineStr">
@@ -11069,7 +11343,19 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11207,7 +11493,19 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">
@@ -11347,7 +11645,19 @@
       </c>
       <c r="N34" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-013</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O34" s="81" t="inlineStr">

--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
@@ -8004,19 +8004,19 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8158,19 +8158,19 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8312,19 +8312,19 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8464,19 +8464,19 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8613,19 +8613,19 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8763,19 +8763,19 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8916,19 +8916,19 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -9064,19 +9064,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9212,19 +9212,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9508,19 +9508,19 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9661,23 +9661,23 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134478
-CFTS084-134479
-CFTS084-134480
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949458
+CFTS084-4949459
+CFTS084-4949461
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9815,23 +9815,23 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134478
-CFTS084-134479
-CFTS084-134480
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949458
+CFTS084-4949459
+CFTS084-4949461
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9970,20 +9970,20 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -10121,20 +10121,20 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10274,19 +10274,19 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10428,19 +10428,19 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10579,19 +10579,19 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10732,19 +10732,19 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10886,19 +10886,19 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -11039,19 +11039,19 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -11193,19 +11193,19 @@
       </c>
       <c r="N31" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O31" s="177" t="inlineStr">
@@ -11343,19 +11343,19 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11493,19 +11493,19 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">
@@ -11645,19 +11645,19 @@
       </c>
       <c r="N34" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O34" s="81" t="inlineStr">
